--- a/artfynd/A 50228-2020 artfynd.xlsx
+++ b/artfynd/A 50228-2020 artfynd.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Johansson, Jonas Nilsson</t>
+          <t>Bengt Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 50228-2020 artfynd.xlsx
+++ b/artfynd/A 50228-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122960058</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 50228-2020 artfynd.xlsx
+++ b/artfynd/A 50228-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122960058</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
